--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-7B-Instruct-v0.3/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-7B-Instruct-v0.3/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -453,13 +453,13 @@
         <v>83</v>
       </c>
       <c r="D3">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="E3">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <v>426</v>
